--- a/tests/fixtures/extract_corpus_v2/dev/bundle_vv40_cht_004/extracted.xlsx
+++ b/tests/fixtures/extract_corpus_v2/dev/bundle_vv40_cht_004/extracted.xlsx
@@ -490,6 +490,11 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="K3" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="L3" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -756,6 +761,46 @@
       </text>
     </comment>
     <comment ref="I7" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="A8" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="B8" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="D8" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="E8" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="F8" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="G8" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="H8" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="I8" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
       </text>
@@ -1403,12 +1448,12 @@
       </c>
       <c r="B3" s="39" t="inlineStr">
         <is>
-          <t>Predict peak tissue temperature and lesion depth to support RF ablation catheter labeling claims</t>
+          <t>Predict peak tissue temperature at 2 mm depth and lesion depth during RF ablation to support device labeling</t>
         </is>
       </c>
       <c r="C3" s="39" t="inlineStr">
         <is>
-          <t>The conjugate heat transfer (CHT) model predicts peak tissue temperature at 2 mm depth and lesion depth after 30–60 s of RF energy delivery (20–35 W, 0.10–0.30 m/s blood crossflow, 10–25 g contact force, 17–30 mL/min saline irrigation). Results support labeling of thermal safety margins and recommended power/flow envelopes for a 3.5 mm irrigated RF ablation catheter tip. Not intended for patient-specific planning or use above 65 °C at 2 mm depth.</t>
+          <t>Conjugate heat transfer model of a 3.5 mm irrigated RF ablation tip used to predict peak tissue temperature at 2 mm depth and lesion depth after 30–60 s RF energy delivery. Results support labeling claims (thermal safety margin and recommended power/flow envelope) for a cardiac ablation catheter. Not intended for direct patient-specific planning. Operating envelope: 20–35 W, 0.10–0.30 m/s blood crossflow, 10–25 g contact force, 17–30 mL/min irrigation.</t>
         </is>
       </c>
       <c r="D3" s="39" t="inlineStr">
@@ -1446,9 +1491,9 @@
           <t>Date of this assessment (YYYY-MM-DD)</t>
         </is>
       </c>
-      <c r="K3" s="22" t="inlineStr">
-        <is>
-          <t>DOI, report number, or URI</t>
+      <c r="K3" s="39" t="inlineStr">
+        <is>
+          <t>report.md</t>
         </is>
       </c>
       <c r="L3" s="40" t="inlineStr">
@@ -2044,7 +2089,7 @@
       </c>
       <c r="B3" s="39" t="inlineStr">
         <is>
-          <t>Thermal Safety Labeling Requirement</t>
+          <t>Thermal Safety Margin Labeling Requirement</t>
         </is>
       </c>
       <c r="C3" s="22" t="inlineStr">
@@ -2054,7 +2099,7 @@
       </c>
       <c r="D3" s="39" t="inlineStr">
         <is>
-          <t>Model must predict peak tissue temperature at 2 mm depth and lesion depth within the validated operating envelope (20–35 W, 0.10–0.30 m/s, 10–25 g, 17–30 mL/min) with sufficient accuracy to support labeling claims; probability of exceeding 65 °C at 2 mm must be demonstrably low (target &lt;5%)</t>
+          <t>Model must predict peak tissue temperature at 2 mm depth and lesion depth within the validated operating envelope (20–35 W, 0.10–0.30 m/s, 10–25 g, 17–30 mL/min) to support labeling claims; probability of exceeding 65 °C at 2 mm depth must remain below acceptable threshold to prevent steam-pop events.</t>
         </is>
       </c>
       <c r="E3" s="22" t="inlineStr">
@@ -2076,13 +2121,13 @@
       </c>
       <c r="B4" s="41" t="inlineStr">
         <is>
-          <t>Irrigated RF Ablation Tip CHT Model v1.6.2</t>
+          <t>Irrigated RF Tip CHT Model v1.6.2</t>
         </is>
       </c>
       <c r="C4" s="24" t="n"/>
       <c r="D4" s="41" t="inlineStr">
         <is>
-          <t>Ansys Fluent 2024R1 conjugate heat transfer model coupling incompressible k–ω SST fluid flow with transient solid conduction (Pennes perfusion) and volumetric RF heat source; covers tip, saline irrigation, blood crossflow, and myocardial tissue</t>
+          <t>Conjugate heat transfer model implemented in Ansys Fluent 2024R1 using k–ω SST turbulence, transient conduction with Pennes perfusion term, and volumetric RF heat source calibrated from EM analysis and fixture measurements.</t>
         </is>
       </c>
       <c r="E4" s="33" t="n"/>
@@ -2102,7 +2147,7 @@
       <c r="C5" s="24" t="n"/>
       <c r="D5" s="41" t="inlineStr">
         <is>
-          <t>12 ex vivo porcine myocardium ablation runs (n=3 repeats at 4 operating points spanning 20/25/35 W and 0.10/0.20/0.30 m/s) with Type T thermocouple and IR camera measurements of tissue temperature and lesion depth</t>
+          <t>12 bench test runs on ex vivo porcine myocardium spanning 20/25/35 W and 0.10/0.20/0.30 m/s blood crossflow (n=3 repeats each), with Type T thermocouple measurements at 2 mm depth and IR surface mapping; instrument uncertainties ±0.3 °C (TC) and ±0.2 °C (IR).</t>
         </is>
       </c>
       <c r="E5" s="33" t="n"/>
@@ -2122,7 +2167,7 @@
       <c r="C6" s="24" t="n"/>
       <c r="D6" s="41" t="inlineStr">
         <is>
-          <t>Six independent gel-phantom runs at 25 W used to calibrate the EM-to-thermal source scaling factor; posterior uncertainty 4.2% (95% CI)</t>
+          <t>Six independent gel-phantom runs at 25 W used to calibrate the EM-to-thermal source scaling factor; resulting factor uncertainty 4.2% (95% CI).</t>
         </is>
       </c>
       <c r="E6" s="33" t="n"/>
@@ -2272,7 +2317,7 @@
     <row r="3" ht="32.8" customHeight="1" s="18">
       <c r="A3" s="39" t="inlineStr">
         <is>
-          <t>Mesh Convergence and GCI Study</t>
+          <t>Mesh Convergence and Spatial Discretization Study</t>
         </is>
       </c>
       <c r="B3" s="39" t="inlineStr">
@@ -2287,12 +2332,12 @@
       </c>
       <c r="D3" s="39" t="inlineStr">
         <is>
-          <t>Three-level mesh refinement (1.2M, 2.4M, 4.8M cells) with y+ &lt; 1; Richardson extrapolation applied to peak tissue temperature at 2 mm and lesion depth</t>
+          <t>Three-level mesh refinement study (1.2M / 2.4M / 4.8M cells, y+ &lt; 1 at tip, 12 prism layers) assessing grid sensitivity of peak tissue temperature at 2 mm depth and lesion depth. Richardson extrapolation applied.</t>
         </is>
       </c>
       <c r="E3" s="39" t="inlineStr">
         <is>
-          <t>Richardson extrapolated (grid-independent) solution</t>
+          <t>Richardson extrapolation extrapolated solution</t>
         </is>
       </c>
       <c r="F3" s="39" t="inlineStr">
@@ -2307,7 +2352,7 @@
       </c>
       <c r="H3" s="39" t="inlineStr">
         <is>
-          <t>GCI 95% = 1.1% for T2mm; GCI 95% = 1.6% for lesion depth</t>
+          <t>GCI 95% = 1.1% for T2mm; GCI 95% = 1.6% for lesion depth; peak T2mm change coarse-to-mid +1.9%, mid-to-fine +0.7%</t>
         </is>
       </c>
       <c r="I3" s="42" t="inlineStr">
@@ -2330,12 +2375,12 @@
       <c r="C4" s="33" t="n"/>
       <c r="D4" s="41" t="inlineStr">
         <is>
-          <t>Baseline time step 1 ms vs. halved step 0.5 ms; effect on T2mm and lesion depth assessed; iterative residuals monitored to convergence</t>
+          <t>Baseline time step Δt = 1 ms compared to halved step Δt = 0.5 ms using backward Euler with second-order transient option; iterative residuals monitored to &lt;1e-6 (energy &lt;1e-8), 12 inner iterations per step.</t>
         </is>
       </c>
       <c r="E4" s="41" t="inlineStr">
         <is>
-          <t>Halved time-step solution; iterative residual targets</t>
+          <t>Halved time step solution</t>
         </is>
       </c>
       <c r="F4" s="41" t="inlineStr">
@@ -2346,7 +2391,7 @@
       <c r="G4" s="33" t="n"/>
       <c r="H4" s="41" t="inlineStr">
         <is>
-          <t>T2mm change 0.8%; lesion depth change 0.5%; energy residuals &lt;1e-8</t>
+          <t>T2mm change 0.8%; lesion depth change 0.5%</t>
         </is>
       </c>
       <c r="I4" s="42" t="inlineStr">
@@ -2358,7 +2403,7 @@
     <row r="5" ht="15" customHeight="1" s="18">
       <c r="A5" s="41" t="inlineStr">
         <is>
-          <t>Method of Manufactured Solutions (MMS) Verification</t>
+          <t>Solver Cross-Check (STAR-CCM+)</t>
         </is>
       </c>
       <c r="B5" s="41" t="inlineStr">
@@ -2369,12 +2414,12 @@
       <c r="C5" s="33" t="n"/>
       <c r="D5" s="41" t="inlineStr">
         <is>
-          <t>MMS applied to transient conduction and coupled slab cases to verify second-order spatial convergence of temperature solution; UDF analytic source accuracy checked</t>
+          <t>One operating point repeated in STAR-CCM+ 2023.3 to confirm solver independence of predictions.</t>
         </is>
       </c>
       <c r="E5" s="41" t="inlineStr">
         <is>
-          <t>Analytic manufactured solution</t>
+          <t>STAR-CCM+ 2023.3 independent solver solution</t>
         </is>
       </c>
       <c r="F5" s="41" t="inlineStr">
@@ -2385,7 +2430,7 @@
       <c r="G5" s="33" t="n"/>
       <c r="H5" s="41" t="inlineStr">
         <is>
-          <t>L2 convergence order 1.98–2.05; UDF error &lt; 0.1%</t>
+          <t>T2mm within 1.4%; lesion depth within 0.9%</t>
         </is>
       </c>
       <c r="I5" s="42" t="inlineStr">
@@ -2397,7 +2442,7 @@
     <row r="6" ht="15" customHeight="1" s="18">
       <c r="A6" s="41" t="inlineStr">
         <is>
-          <t>Cross-Solver Code Verification</t>
+          <t>Method of Manufactured Solutions (MMS) Code Verification</t>
         </is>
       </c>
       <c r="B6" s="41" t="inlineStr">
@@ -2408,12 +2453,12 @@
       <c r="C6" s="33" t="n"/>
       <c r="D6" s="41" t="inlineStr">
         <is>
-          <t>One operating point repeated in STAR-CCM+ 2023.3 and compared to Ansys Fluent result for T2mm and lesion depth</t>
+          <t>MMS applied to transient conduction and coupled slab case to verify second-order spatial accuracy of the Fluent implementation; UDF heat source verified against analytic solution.</t>
         </is>
       </c>
       <c r="E6" s="41" t="inlineStr">
         <is>
-          <t>STAR-CCM+ 2023.3 independent solver result</t>
+          <t>Analytic manufactured solution</t>
         </is>
       </c>
       <c r="F6" s="41" t="inlineStr">
@@ -2424,7 +2469,7 @@
       <c r="G6" s="33" t="n"/>
       <c r="H6" s="41" t="inlineStr">
         <is>
-          <t>T2mm within 1.4%; lesion depth within 0.9%</t>
+          <t>L2 convergence order 1.98–2.05 for temperature; UDF analytic source error &lt;0.1%</t>
         </is>
       </c>
       <c r="I6" s="42" t="inlineStr">
@@ -2436,7 +2481,7 @@
     <row r="7" ht="15" customHeight="1" s="18">
       <c r="A7" s="41" t="inlineStr">
         <is>
-          <t>Ex Vivo Bench Validation — Temperature and Lesion Depth</t>
+          <t>Ex Vivo Porcine Myocardium Validation</t>
         </is>
       </c>
       <c r="B7" s="41" t="inlineStr">
@@ -2447,12 +2492,12 @@
       <c r="C7" s="33" t="n"/>
       <c r="D7" s="41" t="inlineStr">
         <is>
-          <t>Model predictions of T2mm and lesion depth compared to thermocouple and IR camera measurements across 12 ex vivo porcine myocardium test points spanning the full labeling envelope (20–35 W, 0.10–0.30 m/s)</t>
+          <t>Model predictions of T2mm and lesion depth compared against 12 ex vivo porcine bench test runs spanning the full intended operating envelope (20/25/35 W, 0.10/0.20/0.30 m/s). Péclet, Biot, and saline jet Reynolds numbers matched within 7–10%. No systematic bias with power or flow detected.</t>
         </is>
       </c>
       <c r="E7" s="41" t="inlineStr">
         <is>
-          <t>Type T thermocouple (±0.3 °C) and IR camera (±0.2 °C) measurements; lesion depth physical measurement</t>
+          <t>Ex vivo porcine myocardium thermocouple and IR camera measurements</t>
         </is>
       </c>
       <c r="F7" s="41" t="inlineStr">
@@ -2462,12 +2507,12 @@
       </c>
       <c r="G7" s="41" t="inlineStr">
         <is>
-          <t>Latin hypercube sampling (n=200) with mesh-correction; instrument and placement uncertainties propagated; posterior predictive checks</t>
+          <t>Instrument uncertainty characterization (±0.3 °C TC, ±0.2 °C IR); spatial placement uncertainty ±0.2 mm; 200-sample Latin hypercube propagation with mesh correction; posterior predictive checks</t>
         </is>
       </c>
       <c r="H7" s="41" t="inlineStr">
         <is>
-          <t>T2mm MAE = 0.9 °C, RMSE = 1.1 °C; lesion depth MAE = 0.6 mm (8.4%); no systematic bias (p&gt;0.2); 95% interval for worst-case T2mm = 61.8–64.9 °C; P(T2mm &gt; 65 °C) &lt; 2%</t>
+          <t>MAE T2mm = 0.9 °C; RMSE T2mm = 1.1 °C; lesion depth MAE = 0.6 mm (8.4%); p &gt; 0.2 for bias with power or flow</t>
         </is>
       </c>
       <c r="I7" s="42" t="inlineStr">
@@ -2477,14 +2522,47 @@
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="18">
-      <c r="A8" s="24" t="n"/>
-      <c r="B8" s="24" t="n"/>
+      <c r="A8" s="41" t="inlineStr">
+        <is>
+          <t>Uncertainty Propagation and Decision Metric Assessment</t>
+        </is>
+      </c>
+      <c r="B8" s="41" t="inlineStr">
+        <is>
+          <t>ValidationResult</t>
+        </is>
+      </c>
       <c r="C8" s="33" t="n"/>
-      <c r="D8" s="33" t="n"/>
-      <c r="E8" s="25" t="n"/>
-      <c r="F8" s="33" t="n"/>
-      <c r="G8" s="33" t="n"/>
-      <c r="H8" s="33" t="n"/>
+      <c r="D8" s="41" t="inlineStr">
+        <is>
+          <t>200 Latin hypercube samples on mid-mesh with mesh correction propagated measured input distributions to derive 95% predictive interval for T2mm and lesion depth at worst-case operating point within labeling envelope (35 W, 0.10 m/s, 10 g, 17 mL/min). Combined uncertainty budget includes instrument error, placement tolerance, and source-scale uncertainty.</t>
+        </is>
+      </c>
+      <c r="E8" s="41" t="inlineStr">
+        <is>
+          <t>Decision threshold of 65 °C at 2 mm depth</t>
+        </is>
+      </c>
+      <c r="F8" s="41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G8" s="41" t="inlineStr">
+        <is>
+          <t>Latin hypercube sampling; Sobol sensitivity indices; Morris screening; posterior predictive checks</t>
+        </is>
+      </c>
+      <c r="H8" s="41" t="inlineStr">
+        <is>
+          <t>T2mm 95% CI: 61.8–64.9 °C; P(T2mm &gt; 65 °C) &lt; 2%; lesion depth 95% CI: 4.7–6.1 mm</t>
+        </is>
+      </c>
+      <c r="I8" s="42" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="18">
       <c r="A9" s="24" t="n"/>
@@ -2687,16 +2765,16 @@
         <v>4</v>
       </c>
       <c r="D5" s="41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E5" s="42" t="inlineStr">
         <is>
-          <t>Commercial solver with documented QA; regression testing; version control; independent reproducibility check</t>
+          <t>Commercial solver with documented QA, regression testing, version control, and independent reproducibility check</t>
         </is>
       </c>
       <c r="F5" s="41" t="inlineStr">
         <is>
-          <t>Ansys Fluent 2024R1 used in double precision. UDF subjected to code review and unit tests with 100% branch coverage. CI pipeline includes regression tests on 9 cases. Configuration managed in Git (tag v1.6.2) with Fluent case hash; run logs and post-processing scripts archived in DVC. Cross-platform reproducibility confirmed: two clusters (AMD EPYC vs Intel Xeon) matched peak T within 0.05 °C. External SME (Dr. L. Chen) audited setup and case files; comments resolved via CR-142.</t>
+          <t>Ansys Fluent 2024R1 double precision used as commercial solver. UDF code reviewed with 100% branch coverage unit tests. CI pipeline includes regression tests on 9 cases. Configuration managed in Git (tag v1.6.2; Fluent case hash archived in DVC). Reproducibility confirmed across two hardware platforms (AMD EPYC vs Intel Xeon) with peak T matching within 0.05 °C. External audit by Dr. L. Chen (CR-142 resolved).</t>
         </is>
       </c>
       <c r="G5" s="41" t="inlineStr">
@@ -2724,12 +2802,12 @@
       </c>
       <c r="E6" s="42" t="inlineStr">
         <is>
-          <t>Comparison to analytical solutions or MMS demonstrating correct order of convergence; benchmark problem</t>
+          <t>Demonstration of correct order of accuracy on governing equations via MMS or equivalent benchmark</t>
         </is>
       </c>
       <c r="F6" s="41" t="inlineStr">
         <is>
-          <t>MMS applied to transient conduction and coupled slab problems; L2 spatial convergence order 1.98–2.05 (expected second order confirmed). UDF returns analytic source within 0.1%. Independent cross-solver check against STAR-CCM+ 2023.3 at one operating point (T2mm within 1.4%, lesion depth within 0.9%) provides additional code-level assurance.</t>
+          <t>MMS applied to transient conduction and a coupled slab case; L2 convergence order 1.98–2.05 confirms second-order spatial accuracy. UDF time-varying heat source verified analytically to within 0.1%. Energy balance continuity at fluid-solid interface satisfied to within 0.2% across all runs. Independent solver cross-check with STAR-CCM+ 2023.3 at one operating point shows T2mm within 1.4% and lesion depth within 0.9%.</t>
         </is>
       </c>
       <c r="G6" s="41" t="inlineStr">
@@ -2757,12 +2835,12 @@
       </c>
       <c r="E7" s="42" t="inlineStr">
         <is>
-          <t>Mesh convergence study with GCI reported; time-step sensitivity demonstrated</t>
+          <t>Mesh convergence demonstrated with GCI &lt; 3% for primary QoIs; time step sensitivity documented</t>
         </is>
       </c>
       <c r="F7" s="41" t="inlineStr">
         <is>
-          <t>Three-level mesh refinement (1.2M / 2.4M / 4.8M cells) with y+ &lt; 1 and 12 prism layers. Richardson extrapolation yields GCI 95% = 1.1% for T2mm and 1.6% for lesion depth. Time-step sensitivity: halving Δt from 1 ms to 0.5 ms changes T2mm by 0.8% and lesion depth by 0.5%. Backward Euler with second-order transient option tested. Mesh correction applied to UQ propagation runs.</t>
+          <t>Three-level mesh refinement (1.2M/2.4M/4.8M cells) with y+ &lt; 1 at tip and 12 prism layers. Richardson extrapolation yields GCI 95% = 1.1% for T2mm and 1.6% for lesion depth. Coarse-to-mid change +1.9%, mid-to-fine +0.7% demonstrating monotonic convergence. Time step halving (1 ms to 0.5 ms) changes T2mm by 0.8% and lesion depth by 0.5%. Mesh correction applied in LHS uncertainty propagation.</t>
         </is>
       </c>
       <c r="G7" s="41" t="inlineStr">
@@ -2790,12 +2868,12 @@
       </c>
       <c r="E8" s="42" t="inlineStr">
         <is>
-          <t>Residual targets documented and met; convergence monitoring per time step</t>
+          <t>Iterative residuals below defined thresholds; convergence monitoring documented</t>
         </is>
       </c>
       <c r="F8" s="41" t="inlineStr">
         <is>
-          <t>Iterative residuals &lt; 1e-6 (energy &lt; 1e-8) per time step; 12 inner iterations per step ensures stable norms. Residual targets explicitly stated and monitored. Energy balance check: interfacial heat flux continuity satisfied to within 0.2% in all runs.</t>
+          <t>Iterative residuals &lt;1e-6 (energy &lt;1e-8) achieved per time step. 12 inner iterations per step documented as ensuring stable convergence norms. Backward Euler with second-order transient option verified. Residual targets explicitly stated and applied uniformly across all runs.</t>
         </is>
       </c>
       <c r="G8" s="41" t="inlineStr">
@@ -2823,12 +2901,12 @@
       </c>
       <c r="E9" s="42" t="inlineStr">
         <is>
-          <t>Independent review of model setup; boundary condition and mesh quality verification documented</t>
+          <t>Independent review of model setup, boundary conditions, mesh quality, and post-processing; configuration management</t>
         </is>
       </c>
       <c r="F9" s="41" t="inlineStr">
         <is>
-          <t>External SME Dr. L. Chen (not on development team) audited model setup and three case files; all comments resolved (CR-142). Mesh quality checked (y+ &lt; 1, 12 prism layers). Boundary conditions verified against test protocol with NIST-traceable calibrations. Reproducibility confirmed across two compute clusters. Configuration locked in Git with case hash.</t>
+          <t>External SME review by Dr. L. Chen (not on development team) audited setup and three case files; comments resolved per CR-142. Git version control (tag v1.6.2) and DVC archiving of run logs and post-processing scripts. Boundary conditions traceable to NIST-calibrated instruments. Mesh quality documented (y+ &lt; 1, 12 prism layers). Triplicate reproducibility runs vary &lt;0.3 °C with identical inputs.</t>
         </is>
       </c>
       <c r="G9" s="41" t="inlineStr">
@@ -2856,12 +2934,12 @@
       </c>
       <c r="E10" s="42" t="inlineStr">
         <is>
-          <t>Governing equations and turbulence model justified; key assumptions documented with rationale and scope limitations</t>
+          <t>Governing equations justified for physics regime; turbulence model selection rationalized; known limitations documented</t>
         </is>
       </c>
       <c r="F10" s="41" t="inlineStr">
         <is>
-          <t>Conjugate heat transfer with incompressible k–ω SST at Re 300–900 is appropriate and selection is stated. Pennes perfusion term used for tissue. RF deposition modeled as volumetric heat source calibrated to fixture measurements from separate EM analysis at 500 kHz. Key assumptions documented: isotropic tissue conductivity, no boiling/phase change (bounded to &lt;65 °C at 2 mm), conformal contact gap, radiation neglected. Limitations explicitly listed (no boiling, no patient-specific geometry, no tissue anisotropy). Quantitative justification for turbulence model selection and boiling exclusion threshold beyond operating bound is adequate but not formally benchmarked against higher-fidelity models.</t>
+          <t>k–ω SST turbulence model selected for Re ≈ 300–900 near tip (transitional regime appropriate). Pennes perfusion term included in tissue conduction. RF power deposition as volumetric heat source informed by separate 500 kHz EM analysis and calibrated to fixture. Known limitations explicitly documented: no boiling/steam-pocket modeling, no tissue anisotropy, no patient-specific vascular geometry, bounded to &lt;65 °C at 2 mm. Isotropic conductivity assumption noted. Radiation neglected with justification. Turbulence model selection rationale not exhaustively benchmarked against alternatives, preventing level 4.</t>
         </is>
       </c>
       <c r="G10" s="41" t="inlineStr">
@@ -2889,12 +2967,12 @@
       </c>
       <c r="E11" s="42" t="inlineStr">
         <is>
-          <t>Material properties from testing or traceable literature; boundary conditions from calibrated measurements; input uncertainties characterized</t>
+          <t>Material properties, boundary conditions, and geometry from measured/calibrated sources with uncertainty characterization</t>
         </is>
       </c>
       <c r="F11" s="41" t="inlineStr">
         <is>
-          <t>Geometry from vendor CAD (rev D) and CMM scan (tolerances ±0.1 mm). Boundary conditions (blood crossflow 0.10–0.30 m/s, irrigation 17–30 mL/min, RF power 20–35 W, contact force 10–25 g) measured per protocol with NIST-traceable calibrations. Tissue conductivity (0.52–0.72 S/m), thermal conductivity (0.53 W/m-K), and perfusion rate (0.004–0.012 s⁻¹) from literature with posterior estimates from calibration. EM-to-thermal source scaling factor calibrated from six gel-phantom runs; uncertainty 4.2% (95% CI). Global sensitivity analysis (Morris + Sobol) identifies dominant inputs: perfusion rate, contact gap, RF source scale.</t>
+          <t>Geometry from vendor CAD rev D and CMM scan with tolerances ±0.1 mm. Boundary conditions (blood crossflow, saline flow, RF power, contact force) measured per protocol with NIST-traceable calibrations. Tissue conductivity (0.52–0.72 S/m, temperature dependent), thermal conductivity (0.53 W/m-K), and perfusion (0.004–0.012 s^-1) from literature with posterior calibration. EM-to-thermal source scaling factor calibrated from 6 gel-phantom runs; uncertainty 4.2% (95% CI). Global sensitivity analysis (Morris + Sobol) identifies dominant inputs: perfusion (μ*=0.31), contact force gap (μ*=0.27), RF source scale (μ*=0.22).</t>
         </is>
       </c>
       <c r="G11" s="41" t="inlineStr">
@@ -2922,12 +3000,12 @@
       </c>
       <c r="E12" s="42" t="inlineStr">
         <is>
-          <t>Adequate number of specimens with statistical characterization; production-representative samples; sample size justified</t>
+          <t>Sufficient specimen numbers with statistical characterization; production-representative samples; sample size justification</t>
         </is>
       </c>
       <c r="F12" s="41" t="inlineStr">
         <is>
-          <t>12 ex vivo porcine myocardium runs with n=3 repeats at each of 4 operating conditions. Porcine myocardium is an accepted surrogate for cardiac tissue in ablation bench testing. Triplicate repeatability confirmed (T2mm variation &lt;0.3 °C). No formal sample size justification or statistical power calculation documented. Production-representative tissue characterization is not explicitly stated. Sample count is modest but spans the full operating envelope.</t>
+          <t>12 ex vivo porcine myocardium runs with n=3 repeats at each of 4 power-flow combinations (20/25/35 W × 0.10/0.20/0.30 m/s). Triplicate repeats allow within-condition variability assessment. Porcine myocardium is standard surrogate for cardiac tissue in ablation studies. No formal sample size justification or statistical power analysis documented. No characterization of inter-specimen biological variability reported. Level 4 not reached due to absence of explicit statistical adequacy justification.</t>
         </is>
       </c>
       <c r="G12" s="41" t="inlineStr">
@@ -2955,12 +3033,12 @@
       </c>
       <c r="E13" s="42" t="inlineStr">
         <is>
-          <t>Calibrated instrumentation; controlled environment; measurement uncertainties reported; test standard referenced</t>
+          <t>Calibrated instrumentation, controlled environment, measurement uncertainty quantified, traceable to standards</t>
         </is>
       </c>
       <c r="F13" s="41" t="inlineStr">
         <is>
-          <t>Type T thermocouples (40 AWG, ±0.3 °C) and IR camera (±0.2 °C) used with NIST-traceable calibrations for mass and flow benches. Spatial placement uncertainty ±0.2 mm. Tip force and insertion angle matched to ±2 g and ±3°. Instrument uncertainties explicitly stated. Test conditions (blood crossflow, irrigation rate, RF power, contact force) measured per documented protocol. No specific ASTM/ISO test standard cited, but calibration traceability and measurement uncertainty are well-documented.</t>
+          <t>Type T 40 AWG thermocouples at 2 mm depth (±0.3 °C) and IR camera for surface mapping (±0.2 °C). Spatial placement uncertainty ±0.2 mm documented. NIST-traceable mass and flow bench calibrations for boundary condition instruments. Tip force and insertion angle matched to ±2 g and ±3°. All measurements per documented test protocol. Instrument uncertainty budgets explicitly stated and propagated into validation comparison.</t>
         </is>
       </c>
       <c r="G13" s="41" t="inlineStr">
@@ -2988,12 +3066,12 @@
       </c>
       <c r="E14" s="42" t="inlineStr">
         <is>
-          <t>Model inputs demonstrated to match experimental conditions; measurement uncertainty propagated to input matching</t>
+          <t>Quantitative demonstration that model inputs match experimental test conditions including uncertainty propagation</t>
         </is>
       </c>
       <c r="F14" s="41" t="inlineStr">
         <is>
-          <t>Péclet and Biot numbers within 7% of in silico values; saline jet Reynolds number within 10%. Tip force and insertion angle matched to ±2 g and ±3°. Boundary conditions in the model set to match test protocol measurements. Input uncertainty from measurements propagated through 200 Latin hypercube samples on mid-mesh with mesh-correction. Combined uncertainty budget includes instrument error, placement tolerance, and source-scale uncertainty.</t>
+          <t>Péclet and Biot numbers verified within 7% of in silico values; saline jet Reynolds within 10%. Tip force and insertion angle matched to ±2 g and ±3° respectively. Boundary conditions applied to model from same measured values used in bench tests with traceable calibrations. Input uncertainty distributions derived from measured conditions and propagated through 200-sample LHS. Dimensionless parameter matching confirms physical regime equivalence.</t>
         </is>
       </c>
       <c r="G14" s="41" t="inlineStr">
@@ -3021,12 +3099,12 @@
       </c>
       <c r="E15" s="42" t="inlineStr">
         <is>
-          <t>Quantitative error metrics reported across multiple comparison points; statistical validation metrics; uncertainty bands on predictions</t>
+          <t>Quantitative error metrics across multiple operating points; uncertainty bands reported; no systematic bias demonstrated</t>
         </is>
       </c>
       <c r="F15" s="41" t="inlineStr">
         <is>
-          <t>Across 12 ex vivo test points: T2mm MAE = 0.9 °C, RMSE = 1.1 °C. Lesion depth MAE = 0.6 mm (8.4%). No systematic bias with power or flow (p &gt; 0.2). Worst-case 95% predictive interval for T2mm = 61.8–64.9 °C; P(T2mm &gt; 65 °C) &lt; 2%. Uncertainty budget explicitly combines instrument error, placement tolerance, and source-scale uncertainty with posterior predictive checks. Comparison spans full labeling envelope.</t>
+          <t>Across 12 validation points: MAE T2mm = 0.9 °C, RMSE = 1.1 °C; lesion depth MAE = 0.6 mm (8.4%). No systematic bias with power or flow (p &gt; 0.2). 95% predictive interval for worst-case operating point: T2mm 61.8–64.9 °C, lesion depth 4.7–6.1 mm. Combined uncertainty budget includes instrument error, placement tolerance, source-scale uncertainty, and validation-data noise in posterior predictive checks. Multiple operating points spanning intended envelope assessed.</t>
         </is>
       </c>
       <c r="G15" s="41" t="inlineStr">
@@ -3054,12 +3132,12 @@
       </c>
       <c r="E16" s="42" t="inlineStr">
         <is>
-          <t>QoI directly addresses safety/performance concern; measurable computationally and experimentally</t>
+          <t>QoIs directly measure the safety/performance concern and are measurable both computationally and experimentally</t>
         </is>
       </c>
       <c r="F16" s="41" t="inlineStr">
         <is>
-          <t>QoIs are peak tissue temperature at 2 mm depth (thermal safety margin, steam-pop risk) and lesion depth at 60 s (efficacy). Both are directly linked to labeling claims and clinical risk (steam-pop above 65 °C, under-treatment if lesion too shallow). Both are measurable experimentally (thermocouples, IR camera, post-ablation lesion measurement) and predicted by the model. QoIs are well-matched to the decision context.</t>
+          <t>Primary QoIs are peak tissue temperature at 2 mm depth and lesion depth at 60 s — directly relevant to steam-pop prevention (thermal safety) and treatment adequacy (efficacy) labeling claims. Both QoIs are measured experimentally (thermocouple at 2 mm, post-ablation lesion measurement) and computed directly from the model. Decision threshold of 65 °C at 2 mm is explicitly used as the safety criterion with P(exceedance) &lt; 2% quantified.</t>
         </is>
       </c>
       <c r="G16" s="41" t="inlineStr">
@@ -3087,12 +3165,12 @@
       </c>
       <c r="E17" s="42" t="inlineStr">
         <is>
-          <t>Validation conditions bracket the intended use envelope; same geometry, physics regime, and operating conditions; gaps identified</t>
+          <t>Validation conditions bracket the full intended operating envelope; geometry and physics regime match COU; gaps documented</t>
         </is>
       </c>
       <c r="F17" s="41" t="inlineStr">
         <is>
-          <t>Validation matrix (20/25/35 W, 0.10/0.20/0.30 m/s blood speed) fully brackets the intended labeling envelope (20–35 W, 0.10–0.30 m/s, 10–25 g, 17–30 mL/min). Same 3.5 mm tip geometry used. Ex vivo porcine myocardium is accepted cardiac tissue surrogate. Operating regime (Re 300–900, &lt;65 °C) matches model assumptions. Known gaps explicitly stated: no boiling/steam-pocket modeling, no patient-specific vascular geometry, tissue anisotropy neglected, not valid above 65 °C at 2 mm or for atypical flows &gt;0.5 m/s. Extrapolation beyond validated envelope not claimed.</t>
+          <t>Validation matrix (20/25/35 W, 0.10/0.20/0.30 m/s) fully brackets the intended labeling envelope (20–35 W, 0.10–0.30 m/s, 10–25 g, 17–30 mL/min). Same 3.5 mm irrigated tip geometry used. Ex vivo porcine myocardium is standard cardiac ablation surrogate. Dimensionless parameter matching (Pe, Bi, Re_jet) within 7–10% confirms physics regime equivalence. Known gaps explicitly documented: no boiling, no patient-specific anatomy, no tissue anisotropy, bounded to &lt;65 °C and &lt;0.5 m/s flow. No extrapolation claimed outside validated ranges.</t>
         </is>
       </c>
       <c r="G17" s="41" t="inlineStr">
@@ -3181,7 +3259,7 @@
       </c>
       <c r="B3" s="39" t="inlineStr">
         <is>
-          <t>The CHT model meets all 13 credibility factors at or above the required levels for MRL 4. Numerical verification is thorough (MMS second-order convergence confirmed, GCI 95% &lt; 2% for both QoIs, cross-solver agreement within 1.4%). Validation against 12 ex vivo porcine myocardium test points spanning the full labeling envelope yields T2mm MAE = 0.9 °C and lesion depth MAE = 0.6 mm with no systematic bias. The worst-case 95% predictive interval for T2mm (61.8–64.9 °C) gives P(T2mm &gt; 65 °C) &lt; 2%, satisfying the thermal safety requirement. Known limitations (no boiling, no patient-specific geometry, no tissue anisotropy) are explicitly documented and bounded by the validated operating envelope. The model is accepted as a primary line of evidence alongside bench testing to support labeling submission, provided the stated limitations and operating bounds are included in the labeling documentation.</t>
+          <t>The CHT model for the irrigated RF ablation tip meets or exceeds required credibility levels across all 13 ASME V&amp;V 40 factors for the stated context of use. MMS-verified second-order accuracy, GCI &lt; 2% for primary QoIs, and independent solver cross-check establish strong numerical credibility. Validation against 12 ex vivo porcine runs spanning the full intended envelope yields MAE of 0.9 °C for T2mm and 0.6 mm for lesion depth with no systematic bias. Worst-case 95% predictive interval (61.8–64.9 °C) keeps P(T2mm &gt; 65 °C) below 2%, satisfying the thermal safety criterion. The validation matrix fully brackets the labeling envelope and no extrapolation is claimed. Known limitations (no boiling, no tissue anisotropy, no patient-specific anatomy, bounded to &lt;65 °C and &lt;0.5 m/s) are explicitly documented and operationally bounded by the operating envelope. The model is accepted as a primary line of evidence alongside bench testing for labeling submission, with the stated limitations explicitly included in the submission package.</t>
         </is>
       </c>
       <c r="C3" s="22" t="inlineStr">
